--- a/Result/profitability/2347.xlsx
+++ b/Result/profitability/2347.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.38</v>
+        <v>1.50375</v>
       </c>
       <c r="N2" t="n">
-        <v>4.325</v>
+        <v>4.20875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2875</v>
+        <v>1.36</v>
       </c>
       <c r="N3" t="n">
-        <v>4.32875</v>
+        <v>4.1675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.155</v>
+        <v>1.31</v>
       </c>
       <c r="N4" t="n">
-        <v>4.27125</v>
+        <v>4.15</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.075</v>
+        <v>1.26875</v>
       </c>
       <c r="N5" t="n">
-        <v>4.27875</v>
+        <v>4.165</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>1.055</v>
+        <v>1.155</v>
       </c>
       <c r="N6" t="n">
-        <v>4.25125</v>
+        <v>4.1625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>0.97375</v>
+        <v>1.05875</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2675</v>
+        <v>4.16</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.99125</v>
       </c>
       <c r="N8" t="n">
-        <v>4.22125</v>
+        <v>4.108750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.8175</v>
       </c>
       <c r="N9" t="n">
-        <v>4.18375</v>
+        <v>4.183750000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.80125</v>
+        <v>0.8012499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>4.165</v>
@@ -1772,7 +1772,7 @@
         <v>0.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8312499999999999</v>
+        <v>0.83125</v>
       </c>
       <c r="N11" t="n">
         <v>4.0675</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>201010</v>
+      </c>
+      <c r="D75" t="n">
+        <v>194186</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6824</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4780</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>510</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5290</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3909</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.53875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.22125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5699999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3220338983050846</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2093023255813954</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.962025316455696</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9099999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2111368909512761</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
